--- a/data/sars/alaska/tables/Alaska_2022_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2022_Appendix2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evajuenglingbean/Desktop/Graduate Work/Marine Mammal Stock Assessment/2022/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E47832D-D3E4-7649-BF76-C599AB9AD05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F56F7E-8536-C840-86A7-96D55F7C750F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="19400" windowHeight="19820" xr2:uid="{9A269348-4FBD-DE4C-B188-B83A6F27D67B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>Steller sea lion (Western U.S.)</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Ringed seal (Arctic)</t>
   </si>
   <si>
-    <t>Ribbon seal</t>
-  </si>
-  <si>
     <t>Beluga whale (Beaufort Sea)</t>
   </si>
   <si>
@@ -172,12 +169,6 @@
     <t>UNDET</t>
   </si>
   <si>
-    <t>(0.2 for U.S.</t>
-  </si>
-  <si>
-    <t>(0.06 in U.S.</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -245,6 +236,66 @@
   </si>
   <si>
     <t>last_survey</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>updated_yn</t>
+  </si>
+  <si>
+    <t>sim_native</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>NEST is best estimate of counts, which have not been corrected for animals at sea during abundance surveys.</t>
+  </si>
+  <si>
+    <t>Survey years = Sea Lion Rock - 2014; St. Paul and St. George Is. - 2014, 2016, 2018; Bogoslof Is. - 2015, 2019.</t>
+  </si>
+  <si>
+    <t>NEST, NMIN, and PBR have been calculated, however, important caveats exist; see SAR text for details.</t>
+  </si>
+  <si>
+    <t>Survey years = 2014, 2016, and 2018. PBR has been calculated, however, important caveats exist; see SAR text for details.</t>
+  </si>
+  <si>
+    <t>NEST is based on counts of individuals identified from photo-ID catalogs.</t>
+  </si>
+  <si>
+    <t>NEST is based on counts of individuals identified from photo-ID catalogs. PBR has been calculated, however, important caveats exist; see SAR text for details.</t>
+  </si>
+  <si>
+    <t>NEST is based on counts of individuals identified from photo-ID catalogs in an analysis of a subset of data from 1958 to 2018.</t>
+  </si>
+  <si>
+    <t>New stock split from Southeast Alaska stock in 2022.</t>
+  </si>
+  <si>
+    <t>NEST has been calculated, however, important caveats exist; see SAR text for details.</t>
+  </si>
+  <si>
+    <t>New SAR following North Pacific humpback whale stock structure changes</t>
+  </si>
+  <si>
+    <t>New SAR following North Pacific humpback whale stock structure changes. NEST has been calculated, however, important caveats exist; see SAR text for details.</t>
+  </si>
+  <si>
+    <t>PBR has been calculated, however, important caveats exist; see SAR text for details.</t>
+  </si>
+  <si>
+    <t>3.4 (0.2 for U.S. waters)</t>
+  </si>
+  <si>
+    <t>5.82 (0.06 in U.S. waters)</t>
+  </si>
+  <si>
+    <t>Ribbon seal (Alaska)</t>
   </si>
 </sst>
 </file>
@@ -728,7 +779,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -738,6 +789,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1114,1728 +1169,2098 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A87FCDF-DCE0-8D4F-A619-B34DBE8AA6EE}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="79.6640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="1"/>
-    <col min="4" max="6" width="10.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="4" width="10.83203125" style="1"/>
+    <col min="5" max="7" width="10.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="1"/>
+    <col min="12" max="13" width="10.83203125" style="1"/>
+    <col min="14" max="14" width="21.1640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="140.83203125" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="2">
         <v>52932</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>52932</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>0.12</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0.1</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>318</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>254</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>37</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="K2">
+        <v>209</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="1">
         <v>2020</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2">
         <v>43201</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>43201</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>0.12</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>2592</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>112</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>24</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="1">
+      <c r="K3">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="1">
         <v>2017</v>
       </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>2019</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="2">
         <v>626618</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>0.2</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>530376</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>0.5</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>11403</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>373</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>3.5</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4">
+        <v>360</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="N4" s="1">
         <v>2021</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="2">
         <v>5588</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>5366</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>0.12</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>0.3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>97</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>90</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>0.4</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="K5">
+        <v>90</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="1">
         <v>2018</v>
       </c>
-      <c r="L5" s="1">
+      <c r="N5" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="1">
         <v>229</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>229</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>0.12</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>0.5</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>7</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="1">
         <v>2018</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" s="1">
         <v>2019</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2">
         <v>44781</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2">
         <v>38254</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>0.12</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>0.7</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>1607</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>20</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>3.8</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="1">
         <v>2017</v>
       </c>
-      <c r="L7" s="1">
+      <c r="N7" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="2">
         <v>8677</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2">
         <v>7609</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>0.12</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>0.5</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>228</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>38</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>0.3</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" s="1">
+      <c r="K8">
+        <v>37</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="1">
         <v>2017</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="2">
         <v>26448</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2">
         <v>22351</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>0.12</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>0.7</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>939</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>127</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>1.2</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="K9">
+        <v>126</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="1">
         <v>2017</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="2">
         <v>44756</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2">
         <v>41776</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>0.12</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>0.5</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>1253</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>413</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>24</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="K10">
+        <v>387</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="1">
         <v>2015</v>
       </c>
-      <c r="L10" s="1">
+      <c r="N10" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="2">
         <v>28411</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2">
         <v>26907</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>0.12</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>0.5</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>807</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>107</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>2.5</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="1">
+      <c r="K11">
+        <v>104</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="1">
         <v>2018</v>
       </c>
-      <c r="L11" s="1">
+      <c r="N11" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="2">
         <v>7455</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2">
         <v>6680</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>0.12</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>0.3</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>120</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>104</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>104</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="1">
         <v>2017</v>
       </c>
-      <c r="L12" s="1">
+      <c r="N12" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="2">
         <v>13388</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2">
         <v>11867</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>0.12</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>0.3</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>214</v>
       </c>
-      <c r="H13" s="1">
-        <v>50</v>
-      </c>
       <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K13" s="1">
+        <v>50</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>50</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="1">
         <v>2016</v>
       </c>
-      <c r="L13" s="1">
+      <c r="N13" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="2">
         <v>13289</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
         <v>11883</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>0.12</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>0.5</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>356</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>77</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="1">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>77</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="1">
         <v>2015</v>
       </c>
-      <c r="L14" s="1">
+      <c r="N14" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2">
         <v>23478</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2">
         <v>21453</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>0.12</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>0.5</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>644</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>69</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15" s="1">
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>69</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="1">
         <v>2015</v>
       </c>
-      <c r="L15" s="1">
+      <c r="N15" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="2">
         <v>27659</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2">
         <v>24854</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>0.12</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>0.5</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>746</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>40</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>40</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="1">
         <v>2015</v>
       </c>
-      <c r="L16" s="1">
+      <c r="N16" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="2">
         <v>461625</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2">
         <v>423237</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>0.12</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <v>25394</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>5254</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>1</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="4">
+        <v>5253</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="N17" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="1">
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="1">
         <v>0.12</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>0.5</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <v>6709</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>1.8</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L18" s="1">
+      <c r="K18" s="4">
+        <v>6707</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="1">
         <v>2020</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="1">
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="1">
         <v>0.12</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>0.5</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>6459</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>5</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="4">
+        <v>6454</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2020</v>
+      </c>
+      <c r="O19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2">
+        <v>184697</v>
+      </c>
+      <c r="E20" s="2">
+        <v>163086</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <v>9785</v>
+      </c>
+      <c r="I20" s="1">
+        <v>163</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K20">
+        <v>162</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" s="1">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="2">
+        <v>39258</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="1">
+        <v>104</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>104</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1992</v>
+      </c>
+      <c r="N21" s="1">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="2">
+        <v>13305</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="E22" s="2">
+        <v>8875</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>178</v>
+      </c>
+      <c r="I22" s="1">
         <v>56</v>
       </c>
-      <c r="L19" s="1">
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>56</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="1">
+        <v>2017</v>
+      </c>
+      <c r="N22" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2">
-        <v>184697</v>
-      </c>
-      <c r="D20" s="2">
-        <v>163086</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="F20" s="1">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2">
+        <v>12269</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="E23" s="2">
+        <v>11112</v>
+      </c>
+      <c r="F23" s="1">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="G23" s="1">
         <v>1</v>
       </c>
-      <c r="G20" s="2">
-        <v>9785</v>
-      </c>
-      <c r="H20" s="1">
-        <v>163</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="1">
+      <c r="H23" s="1">
+        <v>267</v>
+      </c>
+      <c r="I23" s="1">
+        <v>227</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>227</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2017</v>
+      </c>
+      <c r="N23" s="1">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2040</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1645</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>33</v>
+      </c>
+      <c r="I24" s="1">
+        <v>19</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>19</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="1">
+        <v>2016</v>
+      </c>
+      <c r="N24" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="1">
+        <v>279</v>
+      </c>
+      <c r="D25" s="1">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>267</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" s="1">
+        <v>2021</v>
+      </c>
+      <c r="O25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N26" s="1">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1920</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1920</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
-        <v>39258</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="I27" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="1">
+        <v>2016</v>
+      </c>
+      <c r="O27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="1">
+        <v>302</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="1">
+        <v>302</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="1">
+        <v>2018</v>
+      </c>
+      <c r="N28" s="1">
+        <v>2019</v>
+      </c>
+      <c r="O28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="1">
+        <v>587</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="1">
+        <v>587</v>
+      </c>
+      <c r="F29" s="1">
         <v>0.04</v>
       </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="1">
-        <v>104</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K21" s="1">
-        <v>1992</v>
-      </c>
-      <c r="L21" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2">
-        <v>13305</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="D22" s="2">
-        <v>8875</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>178</v>
-      </c>
-      <c r="H22" s="1">
-        <v>56</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K22" s="1">
-        <v>2017</v>
-      </c>
-      <c r="L22" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2">
-        <v>12269</v>
-      </c>
-      <c r="C23" s="1">
-        <v>0.11799999999999999</v>
-      </c>
-      <c r="D23" s="2">
-        <v>11112</v>
-      </c>
-      <c r="E23" s="1">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>267</v>
-      </c>
-      <c r="H23" s="1">
-        <v>227</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K23" s="1">
-        <v>2017</v>
-      </c>
-      <c r="L23" s="1">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2">
-        <v>2040</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1645</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <v>33</v>
-      </c>
-      <c r="H24" s="1">
-        <v>19</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K24" s="1">
-        <v>2016</v>
-      </c>
-      <c r="L24" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1">
-        <v>279</v>
-      </c>
-      <c r="C25" s="1">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D25" s="1">
-        <v>267</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L25" s="1">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F26" s="1">
+      <c r="G29" s="1">
         <v>0.5</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L26" s="1">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2">
-        <v>1920</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1920</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G27" s="1">
-        <v>19</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="I27" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L27" s="1">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1">
-        <v>302</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="1">
-        <v>302</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G28" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K28" s="1">
-        <v>2018</v>
-      </c>
-      <c r="L28" s="1">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1">
-        <v>587</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="1">
-        <v>587</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F29" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>5.9</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0.8</v>
       </c>
       <c r="I29" s="1">
         <v>0.8</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="J29" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="1">
         <v>2012</v>
       </c>
-      <c r="L29" s="1">
+      <c r="N29" s="1">
         <v>2020</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="1">
+        <v>7</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M30" s="1">
+        <v>2019</v>
+      </c>
+      <c r="N30" s="1">
+        <v>2020</v>
+      </c>
+      <c r="O30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="1">
-        <v>7</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="1">
+        <v>349</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="1">
+        <v>349</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="1">
+        <v>2018</v>
+      </c>
+      <c r="N31" s="1">
+        <v>2020</v>
+      </c>
+      <c r="O31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2">
+        <v>26880</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="1">
-        <v>7</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="1">
+        <v>1990</v>
+      </c>
+      <c r="N32" s="1">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1619</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1250</v>
+      </c>
+      <c r="F33" s="1">
         <v>0.04</v>
       </c>
-      <c r="F30" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K30" s="1">
-        <v>2019</v>
-      </c>
-      <c r="L30" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1">
-        <v>349</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="1">
-        <v>349</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="G33" s="1">
         <v>0.5</v>
       </c>
-      <c r="G31" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I31" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K31" s="1">
-        <v>2018</v>
-      </c>
-      <c r="L31" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="2">
-        <v>26880</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F32" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K32" s="1">
-        <v>1990</v>
-      </c>
-      <c r="L32" s="1">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="2">
-        <v>1619</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="D33" s="2">
-        <v>1250</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F33" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>13</v>
-      </c>
-      <c r="H33" s="1">
-        <v>5.6</v>
       </c>
       <c r="I33" s="1">
         <v>5.6</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="J33" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="1">
         <v>2019</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="N33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="1">
         <v>890</v>
       </c>
-      <c r="C34" s="1">
+      <c r="D34" s="1">
         <v>0.37</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <v>610</v>
       </c>
-      <c r="E34" s="1">
+      <c r="F34" s="1">
         <v>0.04</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>0.5</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>6.1</v>
-      </c>
-      <c r="H34" s="1">
-        <v>7.4</v>
       </c>
       <c r="I34" s="1">
         <v>7.4</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="J34" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M34" s="1">
         <v>2019</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="N34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="1">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" s="1">
         <v>0.04</v>
       </c>
-      <c r="F35" s="1">
+      <c r="G35" s="1">
         <v>0.5</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="1">
-        <v>22.2</v>
+      <c r="H35" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="I35" s="1">
         <v>22.2</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K35" s="1">
+      <c r="J35" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="1">
         <v>1997</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="N35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="2">
+        <v>31046</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I36" s="1">
+        <v>72</v>
+      </c>
+      <c r="J36" s="1">
+        <v>72</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M36" s="1">
+        <v>1998</v>
+      </c>
+      <c r="N36" s="1">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="2">
-        <v>31046</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="1">
+      <c r="I37" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M37" s="1">
+        <v>2008</v>
+      </c>
+      <c r="N37" s="1">
+        <v>2020</v>
+      </c>
+      <c r="O37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" s="1">
         <v>0.04</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G38" s="1">
         <v>0.5</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H36" s="1">
-        <v>72</v>
-      </c>
-      <c r="I36" s="1">
-        <v>72</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K36" s="1">
-        <v>1998</v>
-      </c>
-      <c r="L36" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F37" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K37" s="1">
-        <v>2008</v>
-      </c>
-      <c r="L37" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F38" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H38" s="1">
-        <v>37</v>
       </c>
       <c r="I38" s="1">
         <v>37</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K38" s="1">
+      <c r="J38" s="1">
+        <v>37</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="1">
         <v>2015</v>
       </c>
-      <c r="L38" s="1">
+      <c r="N38" s="1">
         <v>2021</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="O38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I39" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J39" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M39" s="1">
+        <v>2015</v>
+      </c>
+      <c r="N39" s="1">
+        <v>2020</v>
+      </c>
+      <c r="O39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E39" s="1">
+      <c r="B40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40" s="1">
         <v>0.04</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G40" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N40" s="1">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" s="1">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" s="1">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1084</v>
+      </c>
+      <c r="D43" s="1">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1007</v>
+      </c>
+      <c r="F43" s="1">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="G43" s="1">
         <v>0.1</v>
       </c>
-      <c r="H39" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="I39" s="1">
-        <v>3.3</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K39" s="1">
-        <v>2015</v>
-      </c>
-      <c r="L39" s="1">
+      <c r="H43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="K43">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O43" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="2">
+        <v>11278</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E44" s="2">
+        <v>7265</v>
+      </c>
+      <c r="F44" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H44" s="1">
+        <v>127</v>
+      </c>
+      <c r="I44" s="1">
+        <v>27.09</v>
+      </c>
+      <c r="J44" s="1">
+        <v>8.39</v>
+      </c>
+      <c r="K44">
+        <v>0.18</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" s="1">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="K45">
+        <v>0.01</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M46" s="1">
+        <v>2013</v>
+      </c>
+      <c r="N46" s="1">
         <v>2020</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="O46" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F47" s="1">
         <v>0.04</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G47" s="1">
         <v>0.5</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L40" s="1">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="H47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N47" s="1">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="1">
+        <v>31</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="E48" s="1">
+        <v>26</v>
+      </c>
+      <c r="F48" s="1">
         <v>0.04</v>
       </c>
-      <c r="F41" s="1">
+      <c r="G48" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M48" s="1">
+        <v>2008</v>
+      </c>
+      <c r="N48" s="1">
+        <v>2020</v>
+      </c>
+      <c r="O48" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="2">
+        <v>14025</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="E49" s="2">
+        <v>11603</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="G49" s="1">
         <v>0.5</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L41" s="1">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E42" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F42" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L42" s="1">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="2">
-        <v>1084</v>
-      </c>
-      <c r="C43" s="1">
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="D43" s="2">
-        <v>1007</v>
-      </c>
-      <c r="E43" s="1">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="F43" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I43" s="1">
-        <v>1.2E-2</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="2">
-        <v>11278</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="D44" s="2">
-        <v>7265</v>
-      </c>
-      <c r="E44" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F44" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G44" s="1">
-        <v>127</v>
-      </c>
-      <c r="H44" s="1">
-        <v>27.09</v>
-      </c>
-      <c r="I44" s="1">
-        <v>8.39</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="1">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="F45" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G45" s="1" t="s">
+      <c r="H49" s="1">
+        <v>116</v>
+      </c>
+      <c r="I49" s="1">
+        <v>56</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>56</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H45" s="1">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0.36</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F46" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K46" s="1">
-        <v>2013</v>
-      </c>
-      <c r="L46" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E47" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F47" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L47" s="1">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="1">
-        <v>31</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.22600000000000001</v>
-      </c>
-      <c r="D48" s="1">
-        <v>26</v>
-      </c>
-      <c r="E48" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F48" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K48" s="1">
-        <v>2008</v>
-      </c>
-      <c r="L48" s="1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="2">
-        <v>14025</v>
-      </c>
-      <c r="C49" s="1">
-        <v>0.22800000000000001</v>
-      </c>
-      <c r="D49" s="2">
-        <v>11603</v>
-      </c>
-      <c r="E49" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F49" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G49" s="1">
-        <v>116</v>
-      </c>
-      <c r="H49" s="1">
-        <v>56</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K49" s="1">
+      <c r="M49" s="1">
         <v>2019</v>
       </c>
-      <c r="L49" s="1">
+      <c r="N49" s="1">
         <v>2021</v>
       </c>
     </row>

--- a/data/sars/alaska/tables/Alaska_2022_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2022_Appendix2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F56F7E-8536-C840-86A7-96D55F7C750F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264DA815-8173-034C-A92F-6E56EA8019EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="19400" windowHeight="19820" xr2:uid="{9A269348-4FBD-DE4C-B188-B83A6F27D67B}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29460" windowHeight="21620" xr2:uid="{9A269348-4FBD-DE4C-B188-B83A6F27D67B}"/>
   </bookViews>
   <sheets>
     <sheet name="Alaska_2022_appendix2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="94">
   <si>
     <t>Steller sea lion (Western U.S.)</t>
   </si>
@@ -289,13 +289,19 @@
     <t>PBR has been calculated, however, important caveats exist; see SAR text for details.</t>
   </si>
   <si>
-    <t>3.4 (0.2 for U.S. waters)</t>
-  </si>
-  <si>
-    <t>5.82 (0.06 in U.S. waters)</t>
-  </si>
-  <si>
     <t>Ribbon seal (Alaska)</t>
+  </si>
+  <si>
+    <t>pbr_notes</t>
+  </si>
+  <si>
+    <t>sim_total_notes</t>
+  </si>
+  <si>
+    <t>0.2 for U.S. waters</t>
+  </si>
+  <si>
+    <t>0.06 in U.S. waters</t>
   </si>
 </sst>
 </file>
@@ -1169,22 +1175,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A87FCDF-DCE0-8D4F-A619-B34DBE8AA6EE}">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="79.6640625" style="1" customWidth="1"/>
     <col min="3" max="4" width="10.83203125" style="1"/>
     <col min="5" max="7" width="10.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" style="1"/>
-    <col min="12" max="13" width="10.83203125" style="1"/>
-    <col min="14" max="14" width="21.1640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="140.83203125" customWidth="1"/>
-    <col min="16" max="16384" width="10.83203125" style="1"/>
+    <col min="8" max="9" width="15.83203125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="17.1640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" style="1"/>
+    <col min="14" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="21.1640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="140.83203125" customWidth="1"/>
+    <col min="18" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1210,28 +1216,34 @@
         <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,29 +1265,29 @@
       <c r="H2" s="1">
         <v>318</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>254</v>
       </c>
-      <c r="J2" s="1">
+      <c r="L2" s="1">
         <v>37</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>209</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="1">
+      <c r="P2" s="1">
         <v>2020</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1297,29 +1309,30 @@
       <c r="H3" s="2">
         <v>2592</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="2"/>
+      <c r="J3" s="1">
         <v>112</v>
       </c>
-      <c r="J3" s="1">
+      <c r="L3" s="1">
         <v>24</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>11</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="1">
         <v>2017</v>
       </c>
-      <c r="N3" s="1">
+      <c r="P3" s="1">
         <v>2019</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1344,29 +1357,30 @@
       <c r="H4" s="2">
         <v>11403</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="2"/>
+      <c r="J4" s="1">
         <v>373</v>
       </c>
-      <c r="J4" s="1">
+      <c r="L4" s="1">
         <v>3.5</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>360</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="1">
+      <c r="P4" s="1">
         <v>2021</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1388,26 +1402,26 @@
       <c r="H5" s="1">
         <v>97</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>90</v>
       </c>
-      <c r="J5" s="1">
+      <c r="L5" s="1">
         <v>0.4</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>90</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" s="1">
         <v>2018</v>
       </c>
-      <c r="N5" s="1">
+      <c r="P5" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1429,29 +1443,29 @@
       <c r="H6" s="1">
         <v>7</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" s="1">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="1">
         <v>2018</v>
       </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
         <v>2019</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1474,26 +1488,27 @@
       <c r="H7" s="2">
         <v>1607</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2"/>
+      <c r="J7" s="1">
         <v>20</v>
       </c>
-      <c r="J7" s="1">
+      <c r="L7" s="1">
         <v>3.8</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="1">
         <v>2017</v>
       </c>
-      <c r="N7" s="1">
+      <c r="P7" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1516,26 +1531,26 @@
       <c r="H8" s="1">
         <v>228</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>38</v>
       </c>
-      <c r="J8" s="1">
+      <c r="L8" s="1">
         <v>0.3</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>37</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="1">
         <v>2017</v>
       </c>
-      <c r="N8" s="1">
+      <c r="P8" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1558,26 +1573,26 @@
       <c r="H9" s="1">
         <v>939</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>127</v>
       </c>
-      <c r="J9" s="1">
+      <c r="L9" s="1">
         <v>1.2</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>126</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O9" s="1">
         <v>2017</v>
       </c>
-      <c r="N9" s="1">
+      <c r="P9" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1600,26 +1615,27 @@
       <c r="H10" s="2">
         <v>1253</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="2"/>
+      <c r="J10" s="1">
         <v>413</v>
       </c>
-      <c r="J10" s="1">
+      <c r="L10" s="1">
         <v>24</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>387</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="1">
         <v>2015</v>
       </c>
-      <c r="N10" s="1">
+      <c r="P10" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1642,26 +1658,26 @@
       <c r="H11" s="1">
         <v>807</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>107</v>
       </c>
-      <c r="J11" s="1">
+      <c r="L11" s="1">
         <v>2.5</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>104</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" s="1">
         <v>2018</v>
       </c>
-      <c r="N11" s="1">
+      <c r="P11" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1684,26 +1700,26 @@
       <c r="H12" s="1">
         <v>120</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>104</v>
       </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>104</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="1">
+      <c r="N12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="1">
         <v>2017</v>
       </c>
-      <c r="N12" s="1">
+      <c r="P12" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1726,26 +1742,26 @@
       <c r="H13" s="1">
         <v>214</v>
       </c>
-      <c r="I13" s="1">
-        <v>50</v>
-      </c>
       <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>50</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13" s="1">
+        <v>50</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>50</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" s="1">
         <v>2016</v>
       </c>
-      <c r="N13" s="1">
+      <c r="P13" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1768,26 +1784,26 @@
       <c r="H14" s="1">
         <v>356</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>77</v>
       </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>77</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="1">
+      <c r="N14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O14" s="1">
         <v>2015</v>
       </c>
-      <c r="N14" s="1">
+      <c r="P14" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1810,26 +1826,26 @@
       <c r="H15" s="1">
         <v>644</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>69</v>
       </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>69</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="1">
+      <c r="N15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O15" s="1">
         <v>2015</v>
       </c>
-      <c r="N15" s="1">
+      <c r="P15" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1852,26 +1868,26 @@
       <c r="H16" s="1">
         <v>746</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>40</v>
       </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16">
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>40</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="1">
+      <c r="N16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O16" s="1">
         <v>2015</v>
       </c>
-      <c r="N16" s="1">
+      <c r="P16" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1894,26 +1910,28 @@
       <c r="H17" s="2">
         <v>25394</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2">
         <v>5254</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="2"/>
+      <c r="L17" s="1">
         <v>1</v>
       </c>
-      <c r="K17" s="4">
+      <c r="M17" s="4">
         <v>5253</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N17" s="1">
+      <c r="P17" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1926,29 +1944,30 @@
       <c r="G18" s="1">
         <v>0.5</v>
       </c>
-      <c r="I18" s="2">
+      <c r="J18" s="2">
         <v>6709</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="2"/>
+      <c r="L18" s="1">
         <v>1.8</v>
       </c>
-      <c r="K18" s="4">
+      <c r="M18" s="4">
         <v>6707</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N18" s="1">
+      <c r="P18" s="1">
         <v>2020</v>
       </c>
-      <c r="O18" t="s">
+      <c r="Q18" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1961,31 +1980,32 @@
       <c r="G19" s="1">
         <v>0.5</v>
       </c>
-      <c r="I19" s="2">
+      <c r="J19" s="2">
         <v>6459</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="2"/>
+      <c r="L19" s="1">
         <v>5</v>
       </c>
-      <c r="K19" s="4">
+      <c r="M19" s="4">
         <v>6454</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N19" s="1">
+      <c r="P19" s="1">
         <v>2020</v>
       </c>
-      <c r="O19" t="s">
+      <c r="Q19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>72</v>
@@ -2005,26 +2025,27 @@
       <c r="H20" s="2">
         <v>9785</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="2"/>
+      <c r="J20" s="1">
         <v>163</v>
       </c>
-      <c r="J20" s="1">
+      <c r="L20" s="1">
         <v>0.9</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>162</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N20" s="1">
+      <c r="P20" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
@@ -2049,26 +2070,26 @@
       <c r="H21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>104</v>
       </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>104</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M21" s="1">
+      <c r="N21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O21" s="1">
         <v>1992</v>
       </c>
-      <c r="N21" s="1">
+      <c r="P21" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -2093,26 +2114,26 @@
       <c r="H22" s="1">
         <v>178</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>56</v>
       </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22">
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>56</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M22" s="1">
+      <c r="N22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O22" s="1">
         <v>2017</v>
       </c>
-      <c r="N22" s="1">
+      <c r="P22" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -2137,26 +2158,26 @@
       <c r="H23" s="1">
         <v>267</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>227</v>
       </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23">
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>227</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M23" s="1">
+      <c r="N23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O23" s="1">
         <v>2017</v>
       </c>
-      <c r="N23" s="1">
+      <c r="P23" s="1">
         <v>2017</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
@@ -2181,26 +2202,26 @@
       <c r="H24" s="1">
         <v>33</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>19</v>
       </c>
-      <c r="J24" s="1">
-        <v>0</v>
-      </c>
-      <c r="K24">
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>19</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M24" s="1">
+      <c r="N24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O24" s="1">
         <v>2016</v>
       </c>
-      <c r="N24" s="1">
+      <c r="P24" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>22</v>
       </c>
@@ -2222,29 +2243,29 @@
       <c r="G25" s="1">
         <v>0.1</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
       <c r="J25" s="1">
         <v>0</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="O25" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="N25" s="1">
+      <c r="P25" s="1">
         <v>2021</v>
       </c>
-      <c r="O25" t="s">
+      <c r="Q25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
@@ -2269,23 +2290,23 @@
       <c r="H26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
       <c r="J26" s="1">
         <v>0</v>
       </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N26" s="1">
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P26" s="1">
         <v>2016</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
@@ -2310,29 +2331,29 @@
       <c r="H27" s="1">
         <v>19</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>1.3</v>
       </c>
-      <c r="J27" s="1">
+      <c r="L27" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N27" s="1">
+      <c r="P27" s="1">
         <v>2016</v>
       </c>
-      <c r="O27" t="s">
+      <c r="Q27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
@@ -2357,29 +2378,29 @@
       <c r="H28" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>0.2</v>
       </c>
-      <c r="J28" s="1">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M28" s="1">
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O28" s="1">
         <v>2018</v>
       </c>
-      <c r="N28" s="1">
+      <c r="P28" s="1">
         <v>2019</v>
       </c>
-      <c r="O28" t="s">
+      <c r="Q28" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
@@ -2404,29 +2425,29 @@
       <c r="H29" s="1">
         <v>5.9</v>
       </c>
-      <c r="I29" s="1">
-        <v>0.8</v>
-      </c>
       <c r="J29" s="1">
         <v>0.8</v>
       </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M29" s="1">
+      <c r="L29" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O29" s="1">
         <v>2012</v>
       </c>
-      <c r="N29" s="1">
+      <c r="P29" s="1">
         <v>2020</v>
       </c>
-      <c r="O29" t="s">
+      <c r="Q29" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
@@ -2448,29 +2469,29 @@
       <c r="G30" s="1">
         <v>0.1</v>
       </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
       <c r="J30" s="1">
         <v>0</v>
       </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1" t="s">
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M30" s="1">
+      <c r="O30" s="1">
         <v>2019</v>
       </c>
-      <c r="N30" s="1">
+      <c r="P30" s="1">
         <v>2020</v>
       </c>
-      <c r="O30" t="s">
+      <c r="Q30" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>28</v>
       </c>
@@ -2495,29 +2516,29 @@
       <c r="H31" s="1">
         <v>3.5</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>0.4</v>
       </c>
-      <c r="J31" s="1">
+      <c r="L31" s="1">
         <v>0.2</v>
       </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M31" s="1">
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O31" s="1">
         <v>2018</v>
       </c>
-      <c r="N31" s="1">
+      <c r="P31" s="1">
         <v>2020</v>
       </c>
-      <c r="O31" t="s">
+      <c r="Q31" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,26 +2563,26 @@
       <c r="H32" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
       <c r="J32" s="1">
         <v>0</v>
       </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M32" s="1">
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O32" s="1">
         <v>1990</v>
       </c>
-      <c r="N32" s="1">
+      <c r="P32" s="1">
         <v>2018</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>30</v>
       </c>
@@ -2586,29 +2607,29 @@
       <c r="H33" s="1">
         <v>13</v>
       </c>
-      <c r="I33" s="1">
-        <v>5.6</v>
-      </c>
       <c r="J33" s="1">
         <v>5.6</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M33" s="1">
+      <c r="L33" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O33" s="1">
         <v>2019</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="P33" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O33" t="s">
+      <c r="Q33" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>31</v>
       </c>
@@ -2633,29 +2654,29 @@
       <c r="H34" s="1">
         <v>6.1</v>
       </c>
-      <c r="I34" s="1">
-        <v>7.4</v>
-      </c>
       <c r="J34" s="1">
         <v>7.4</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1" t="s">
+      <c r="L34" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M34" s="1">
+      <c r="O34" s="1">
         <v>2019</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O34" t="s">
+      <c r="Q34" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
@@ -2677,29 +2698,29 @@
       <c r="H35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I35" s="1">
-        <v>22.2</v>
-      </c>
       <c r="J35" s="1">
         <v>22.2</v>
       </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M35" s="1">
+      <c r="L35" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O35" s="1">
         <v>1997</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="P35" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O35" t="s">
+      <c r="Q35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
@@ -2724,26 +2745,26 @@
       <c r="H36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I36" s="1">
-        <v>72</v>
-      </c>
       <c r="J36" s="1">
         <v>72</v>
       </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="1">
+        <v>72</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M36" s="1">
+      <c r="O36" s="1">
         <v>1998</v>
       </c>
-      <c r="N36" s="1">
+      <c r="P36" s="1">
         <v>2020</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
@@ -2762,29 +2783,29 @@
       <c r="H37" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37" s="1">
         <v>0.4</v>
       </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1" t="s">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M37" s="1">
+      <c r="O37" s="1">
         <v>2008</v>
       </c>
-      <c r="N37" s="1">
+      <c r="P37" s="1">
         <v>2020</v>
       </c>
-      <c r="O37" t="s">
+      <c r="Q37" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>35</v>
       </c>
@@ -2797,29 +2818,29 @@
       <c r="G38" s="1">
         <v>0.5</v>
       </c>
-      <c r="I38" s="1">
-        <v>37</v>
-      </c>
       <c r="J38" s="1">
         <v>37</v>
       </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M38" s="1">
+      <c r="L38" s="1">
+        <v>37</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O38" s="1">
         <v>2015</v>
       </c>
-      <c r="N38" s="1">
+      <c r="P38" s="1">
         <v>2021</v>
       </c>
-      <c r="O38" t="s">
+      <c r="Q38" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
@@ -2832,29 +2853,29 @@
       <c r="G39" s="1">
         <v>0.1</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <v>3.5</v>
       </c>
-      <c r="J39" s="1">
+      <c r="L39" s="1">
         <v>3.3</v>
       </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1" t="s">
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M39" s="1">
+      <c r="O39" s="1">
         <v>2015</v>
       </c>
-      <c r="N39" s="1">
+      <c r="P39" s="1">
         <v>2020</v>
       </c>
-      <c r="O39" t="s">
+      <c r="Q39" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>37</v>
       </c>
@@ -2876,23 +2897,23 @@
       <c r="H40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
       <c r="J40" s="1">
         <v>0</v>
       </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N40" s="1">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P40" s="1">
         <v>2013</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>38</v>
       </c>
@@ -2914,23 +2935,23 @@
       <c r="H41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
       <c r="J41" s="1">
         <v>0</v>
       </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N41" s="1">
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P41" s="1">
         <v>2013</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
@@ -2952,23 +2973,23 @@
       <c r="H42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
       <c r="J42" s="1">
         <v>0</v>
       </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N42" s="1">
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P42" s="1">
         <v>2013</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>40</v>
       </c>
@@ -2990,32 +3011,38 @@
       <c r="G43" s="1">
         <v>0.1</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>89</v>
+      <c r="H43" s="1">
+        <v>3.4</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J43" s="1">
+        <v>5.82</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L43" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="O43" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="P43" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O43" t="s">
+      <c r="Q43" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>41</v>
       </c>
@@ -3040,29 +3067,29 @@
       <c r="H44" s="1">
         <v>127</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44" s="1">
         <v>27.09</v>
       </c>
-      <c r="J44" s="1">
+      <c r="L44" s="1">
         <v>8.39</v>
       </c>
-      <c r="K44">
+      <c r="M44">
         <v>0.18</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M44" s="1" t="s">
+      <c r="N44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O44" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="P44" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O44" t="s">
+      <c r="Q44" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>42</v>
       </c>
@@ -3081,29 +3108,29 @@
       <c r="H45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45" s="1">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J45" s="1">
+      <c r="L45" s="1">
         <v>0.36</v>
       </c>
-      <c r="K45">
+      <c r="M45">
         <v>0.01</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="N45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="O45" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="P45" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O45" s="5" t="s">
+      <c r="Q45" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>43</v>
       </c>
@@ -3116,29 +3143,29 @@
       <c r="G46" s="1">
         <v>0.1</v>
       </c>
-      <c r="I46" s="1">
+      <c r="J46" s="1">
         <v>0.6</v>
       </c>
-      <c r="J46" s="1">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46" s="1" t="s">
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M46" s="1">
+      <c r="O46" s="1">
         <v>2013</v>
       </c>
-      <c r="N46" s="1">
+      <c r="P46" s="1">
         <v>2020</v>
       </c>
-      <c r="O46" t="s">
+      <c r="Q46" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>44</v>
       </c>
@@ -3160,23 +3187,23 @@
       <c r="H47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
       <c r="J47" s="1">
         <v>0</v>
       </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N47" s="1">
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P47" s="1">
         <v>2018</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>45</v>
       </c>
@@ -3198,29 +3225,29 @@
       <c r="G48" s="1">
         <v>0.1</v>
       </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
       <c r="J48" s="1">
         <v>0</v>
       </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48" s="1" t="s">
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M48" s="1">
+      <c r="O48" s="1">
         <v>2008</v>
       </c>
-      <c r="N48" s="1">
+      <c r="P48" s="1">
         <v>2020</v>
       </c>
-      <c r="O48" t="s">
+      <c r="Q48" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>46</v>
       </c>
@@ -3245,22 +3272,22 @@
       <c r="H49" s="1">
         <v>116</v>
       </c>
-      <c r="I49" s="1">
+      <c r="J49" s="1">
         <v>56</v>
       </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49">
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>56</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="N49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M49" s="1">
+      <c r="O49" s="1">
         <v>2019</v>
       </c>
-      <c r="N49" s="1">
+      <c r="P49" s="1">
         <v>2021</v>
       </c>
     </row>
